--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T18:21:29+00:00</t>
+    <t>2026-03-02T13:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2440,7 +2440,7 @@
     <t>The style of appointment or patient that may be booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>https://smart-scheduling-links.org/ValueSet/appointment-type-and-reasons-vs</t>
   </si>
   <si>
     <t>Slot.schedule</t>
@@ -3838,7 +3838,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="58.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="62.265625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -25199,7 +25199,7 @@
         <v>83</v>
       </c>
       <c r="I205" t="s" s="2">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="J205" t="s" s="2">
         <v>22</v>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T13:43:11+00:00</t>
+    <t>2026-03-02T13:46:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T13:46:35+00:00</t>
+    <t>2026-03-02T18:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
